--- a/extenbooks/XS009_extenbook.xlsx
+++ b/extenbooks/XS009_extenbook.xlsx
@@ -865,7 +865,7 @@
         <v>64.38519516355932</v>
       </c>
       <c r="C16" t="n">
-        <v>442.5900830932797</v>
+        <v>442.5900830932796</v>
       </c>
       <c r="D16" t="n">
         <v>506.975278256839</v>
@@ -1019,7 +1019,7 @@
         <v>171.1539591288099</v>
       </c>
       <c r="C27" t="n">
-        <v>928.3262407092184</v>
+        <v>928.3262407092185</v>
       </c>
       <c r="D27" t="n">
         <v>1099.480199838029</v>
@@ -1173,7 +1173,7 @@
         <v>555.6651749830419</v>
       </c>
       <c r="C38" t="n">
-        <v>3800.071121600248</v>
+        <v>3800.071121600247</v>
       </c>
       <c r="D38" t="n">
         <v>4355.736296583289</v>
@@ -1344,7 +1344,7 @@
         <v>8013.034801142843</v>
       </c>
       <c r="D50" t="n">
-        <v>9210.241449349063</v>
+        <v>9210.241449349065</v>
       </c>
     </row>
     <row r="51">
@@ -1352,7 +1352,7 @@
         <v>1993</v>
       </c>
       <c r="B51" t="n">
-        <v>1248.180715356768</v>
+        <v>1248.180715356767</v>
       </c>
       <c r="C51" t="n">
         <v>8456.679308939059</v>
@@ -1411,7 +1411,7 @@
         <v>1528.968573088737</v>
       </c>
       <c r="C55" t="n">
-        <v>10645.46761806426</v>
+        <v>10645.46761806427</v>
       </c>
       <c r="D55" t="n">
         <v>12174.436191153</v>
@@ -1540,7 +1540,7 @@
         <v>19265.16196987102</v>
       </c>
       <c r="D64" t="n">
-        <v>21843.25311156297</v>
+        <v>21843.25311156298</v>
       </c>
     </row>
     <row r="65">
@@ -1593,7 +1593,7 @@
         <v>2726.997261674907</v>
       </c>
       <c r="C68" t="n">
-        <v>21982.08196158393</v>
+        <v>21982.08196158394</v>
       </c>
       <c r="D68" t="n">
         <v>24709.07922325884</v>
@@ -1675,14 +1675,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="B76" t="n">
-        <v>152.542962397858</v>
+        <v>25.1924207661426</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1698,14 +1698,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="B77" t="n">
-        <v>173.2221675300687</v>
+        <v>28.79809743808157</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1721,10 +1721,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="B78" t="n">
-        <v>25.1924207661426</v>
+        <v>28.52277017205926</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1744,14 +1744,14 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="B79" t="n">
-        <v>170.5828337097477</v>
+        <v>35.69829666230825</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1767,14 +1767,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="B80" t="n">
-        <v>195.7752544758903</v>
+        <v>42.23651081882974</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1948</v>
+        <v>1952</v>
       </c>
       <c r="B81" t="n">
-        <v>28.79809743808157</v>
+        <v>44.2476572792157</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1813,14 +1813,14 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1948</v>
+        <v>1953</v>
       </c>
       <c r="B82" t="n">
-        <v>191.6835928065198</v>
+        <v>46.10110690219687</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -1836,14 +1836,14 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1948</v>
+        <v>1954</v>
       </c>
       <c r="B83" t="n">
-        <v>220.4816902446014</v>
+        <v>46.03747911853146</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1949</v>
+        <v>1955</v>
       </c>
       <c r="B84" t="n">
-        <v>28.52277017205926</v>
+        <v>52.78384952113242</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1882,14 +1882,14 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1949</v>
+        <v>1956</v>
       </c>
       <c r="B85" t="n">
-        <v>200.7047696097666</v>
+        <v>58.82817443841661</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -1905,14 +1905,14 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1949</v>
+        <v>1957</v>
       </c>
       <c r="B86" t="n">
-        <v>229.2275397818259</v>
+        <v>61.55584121263325</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -1928,10 +1928,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1950</v>
+        <v>1958</v>
       </c>
       <c r="B87" t="n">
-        <v>35.69829666230825</v>
+        <v>64.38519516355932</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1951,14 +1951,14 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1950</v>
+        <v>1959</v>
       </c>
       <c r="B88" t="n">
-        <v>230.2060065290138</v>
+        <v>71.88719080210795</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -1974,14 +1974,14 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1950</v>
+        <v>1960</v>
       </c>
       <c r="B89" t="n">
-        <v>265.9043031913221</v>
+        <v>75.13160245469801</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -1997,10 +1997,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1951</v>
+        <v>1961</v>
       </c>
       <c r="B90" t="n">
-        <v>42.23651081882974</v>
+        <v>79.95142420211542</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2020,14 +2020,14 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1951</v>
+        <v>1962</v>
       </c>
       <c r="B91" t="n">
-        <v>255.8497941460225</v>
+        <v>85.59891331410986</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2043,14 +2043,14 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="B92" t="n">
-        <v>298.0863049648523</v>
+        <v>92.28682901402844</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="B93" t="n">
-        <v>44.2476572792157</v>
+        <v>98.7398099442203</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2089,14 +2089,14 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1952</v>
+        <v>1965</v>
       </c>
       <c r="B94" t="n">
-        <v>276.7328418152084</v>
+        <v>110.6759004119418</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2112,14 +2112,14 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1952</v>
+        <v>1966</v>
       </c>
       <c r="B95" t="n">
-        <v>320.9804990944241</v>
+        <v>124.3431359766894</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2135,10 +2135,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1953</v>
+        <v>1967</v>
       </c>
       <c r="B96" t="n">
-        <v>46.10110690219687</v>
+        <v>137.2458054841117</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -2158,14 +2158,14 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1953</v>
+        <v>1968</v>
       </c>
       <c r="B97" t="n">
-        <v>296.535558486477</v>
+        <v>150.873037001284</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2181,14 +2181,14 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1953</v>
+        <v>1969</v>
       </c>
       <c r="B98" t="n">
-        <v>342.6366653886739</v>
+        <v>171.1539591288099</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2204,10 +2204,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1954</v>
+        <v>1970</v>
       </c>
       <c r="B99" t="n">
-        <v>46.03747911853146</v>
+        <v>180.5525721624072</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2227,14 +2227,14 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1954</v>
+        <v>1971</v>
       </c>
       <c r="B100" t="n">
-        <v>311.2351026905877</v>
+        <v>192.3602938159656</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2250,14 +2250,14 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1954</v>
+        <v>1972</v>
       </c>
       <c r="B101" t="n">
-        <v>357.2725818091191</v>
+        <v>217.6957407429651</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2273,10 +2273,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1955</v>
+        <v>1973</v>
       </c>
       <c r="B102" t="n">
-        <v>52.78384952113242</v>
+        <v>255.4848400445016</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2296,14 +2296,14 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1955</v>
+        <v>1974</v>
       </c>
       <c r="B103" t="n">
-        <v>347.9833912572905</v>
+        <v>305.8594920722974</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2319,14 +2319,14 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1955</v>
+        <v>1975</v>
       </c>
       <c r="B104" t="n">
-        <v>400.7672407784229</v>
+        <v>319.4743310918299</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1956</v>
+        <v>1976</v>
       </c>
       <c r="B105" t="n">
-        <v>58.82817443841661</v>
+        <v>356.5855886169328</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2365,14 +2365,14 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1956</v>
+        <v>1977</v>
       </c>
       <c r="B106" t="n">
-        <v>391.8473726280085</v>
+        <v>402.9218074965217</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2388,14 +2388,14 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1956</v>
+        <v>1978</v>
       </c>
       <c r="B107" t="n">
-        <v>450.6755470664251</v>
+        <v>448.6215129892695</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2411,10 +2411,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1957</v>
+        <v>1979</v>
       </c>
       <c r="B108" t="n">
-        <v>61.55584121263325</v>
+        <v>512.0243736088548</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2434,14 +2434,14 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1957</v>
+        <v>1980</v>
       </c>
       <c r="B109" t="n">
-        <v>426.5861093605473</v>
+        <v>555.6651749830419</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2457,14 +2457,14 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1957</v>
+        <v>1981</v>
       </c>
       <c r="B110" t="n">
-        <v>488.1419505731806</v>
+        <v>618.2344737387148</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1958</v>
+        <v>1982</v>
       </c>
       <c r="B111" t="n">
-        <v>64.38519516355932</v>
+        <v>632.4657606176995</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2503,14 +2503,14 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1958</v>
+        <v>1983</v>
       </c>
       <c r="B112" t="n">
-        <v>442.5900830932797</v>
+        <v>673.2874813221468</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2526,14 +2526,14 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1958</v>
+        <v>1984</v>
       </c>
       <c r="B113" t="n">
-        <v>506.975278256839</v>
+        <v>745.4861043802233</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2549,10 +2549,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1959</v>
+        <v>1985</v>
       </c>
       <c r="B114" t="n">
-        <v>71.88719080210795</v>
+        <v>816.6092674480941</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2572,14 +2572,14 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1959</v>
+        <v>1986</v>
       </c>
       <c r="B115" t="n">
-        <v>469.2512596112735</v>
+        <v>863.7334582791135</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2595,14 +2595,14 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1959</v>
+        <v>1987</v>
       </c>
       <c r="B116" t="n">
-        <v>541.1384504133814</v>
+        <v>1001.083527467324</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1960</v>
+        <v>1988</v>
       </c>
       <c r="B117" t="n">
-        <v>75.13160245469801</v>
+        <v>1033.037216146162</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2641,14 +2641,14 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1960</v>
+        <v>1989</v>
       </c>
       <c r="B118" t="n">
-        <v>484.9322528829036</v>
+        <v>1085.42604844515</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2664,14 +2664,14 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1960</v>
+        <v>1990</v>
       </c>
       <c r="B119" t="n">
-        <v>560.0638553376016</v>
+        <v>1117.865976544959</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2687,10 +2687,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1961</v>
+        <v>1991</v>
       </c>
       <c r="B120" t="n">
-        <v>79.95142420211542</v>
+        <v>1136.620520775428</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -2710,14 +2710,14 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1961</v>
+        <v>1992</v>
       </c>
       <c r="B121" t="n">
-        <v>503.2776347160874</v>
+        <v>1197.206648206223</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2733,14 +2733,14 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1961</v>
+        <v>1993</v>
       </c>
       <c r="B122" t="n">
-        <v>583.2290589182029</v>
+        <v>1248.180715356767</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2756,10 +2756,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1962</v>
+        <v>1994</v>
       </c>
       <c r="B123" t="n">
-        <v>85.59891331410986</v>
+        <v>1497.309686291692</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2779,14 +2779,14 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1962</v>
+        <v>1995</v>
       </c>
       <c r="B124" t="n">
-        <v>525.4492389980019</v>
+        <v>1398.771225589691</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2802,14 +2802,14 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1962</v>
+        <v>1996</v>
       </c>
       <c r="B125" t="n">
-        <v>611.0481523121117</v>
+        <v>1462.14304339995</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -2825,10 +2825,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1963</v>
+        <v>1997</v>
       </c>
       <c r="B126" t="n">
-        <v>92.28682901402844</v>
+        <v>1528.968573088737</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2848,14 +2848,14 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1963</v>
+        <v>1998</v>
       </c>
       <c r="B127" t="n">
-        <v>548.4317201515985</v>
+        <v>1584.041535971308</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2871,14 +2871,14 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1963</v>
+        <v>1999</v>
       </c>
       <c r="B128" t="n">
-        <v>640.7185491656269</v>
+        <v>1689.702679262337</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -2894,10 +2894,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1964</v>
+        <v>2000</v>
       </c>
       <c r="B129" t="n">
-        <v>98.7398099442203</v>
+        <v>1816.044686363544</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -2917,14 +2917,14 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1964</v>
+        <v>2001</v>
       </c>
       <c r="B130" t="n">
-        <v>584.416740608418</v>
+        <v>1786.616347218415</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2940,14 +2940,14 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1964</v>
+        <v>2002</v>
       </c>
       <c r="B131" t="n">
-        <v>683.1565505526382</v>
+        <v>1874.073582251186</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -2963,10 +2963,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1965</v>
+        <v>2003</v>
       </c>
       <c r="B132" t="n">
-        <v>110.6759004119418</v>
+        <v>1978.6162598011</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -2986,14 +2986,14 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1965</v>
+        <v>2004</v>
       </c>
       <c r="B133" t="n">
-        <v>629.5138499735924</v>
+        <v>2187.029189209532</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3009,14 +3009,14 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1965</v>
+        <v>2005</v>
       </c>
       <c r="B134" t="n">
-        <v>740.1897503855342</v>
+        <v>2394.085629659626</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3032,10 +3032,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1966</v>
+        <v>2006</v>
       </c>
       <c r="B135" t="n">
-        <v>124.3431359766894</v>
+        <v>2578.091141691955</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -3055,14 +3055,14 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1966</v>
+        <v>2007</v>
       </c>
       <c r="B136" t="n">
-        <v>689.3389442732511</v>
+        <v>2676.214530237791</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3078,14 +3078,14 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1966</v>
+        <v>2008</v>
       </c>
       <c r="B137" t="n">
-        <v>813.6820802499406</v>
+        <v>2675.893068192786</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3101,10 +3101,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1967</v>
+        <v>2009</v>
       </c>
       <c r="B138" t="n">
-        <v>137.2458054841117</v>
+        <v>2562.064159856566</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -3124,14 +3124,14 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1967</v>
+        <v>2010</v>
       </c>
       <c r="B139" t="n">
-        <v>753.3311352268145</v>
+        <v>2726.997261674907</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3147,14 +3147,14 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1967</v>
+        <v>2011</v>
       </c>
       <c r="B140" t="n">
-        <v>890.5769407109261</v>
+        <v>2937.530680167656</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3170,14 +3170,14 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1968</v>
+        <v>1946</v>
       </c>
       <c r="B141" t="n">
-        <v>150.873037001284</v>
+        <v>152.542962397858</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3193,10 +3193,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1968</v>
+        <v>1947</v>
       </c>
       <c r="B142" t="n">
-        <v>835.8512661760232</v>
+        <v>170.5828337097477</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -3216,14 +3216,14 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1968</v>
+        <v>1948</v>
       </c>
       <c r="B143" t="n">
-        <v>986.7243031773072</v>
+        <v>191.6835928065198</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3239,14 +3239,14 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1969</v>
+        <v>1949</v>
       </c>
       <c r="B144" t="n">
-        <v>171.1539591288099</v>
+        <v>200.7047696097666</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3262,10 +3262,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1969</v>
+        <v>1950</v>
       </c>
       <c r="B145" t="n">
-        <v>928.3262407092184</v>
+        <v>230.2060065290138</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -3285,14 +3285,14 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1969</v>
+        <v>1951</v>
       </c>
       <c r="B146" t="n">
-        <v>1099.480199838029</v>
+        <v>255.8497941460225</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3308,14 +3308,14 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1970</v>
+        <v>1952</v>
       </c>
       <c r="B147" t="n">
-        <v>180.5525721624072</v>
+        <v>276.7328418152084</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3331,10 +3331,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1970</v>
+        <v>1953</v>
       </c>
       <c r="B148" t="n">
-        <v>1032.410989618403</v>
+        <v>296.535558486477</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -3354,14 +3354,14 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1970</v>
+        <v>1954</v>
       </c>
       <c r="B149" t="n">
-        <v>1212.96356178081</v>
+        <v>311.2351026905877</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3377,14 +3377,14 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1971</v>
+        <v>1955</v>
       </c>
       <c r="B150" t="n">
-        <v>192.3602938159656</v>
+        <v>347.9833912572905</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3400,10 +3400,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1971</v>
+        <v>1956</v>
       </c>
       <c r="B151" t="n">
-        <v>1145.856447448968</v>
+        <v>391.8473726280085</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -3423,14 +3423,14 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1971</v>
+        <v>1957</v>
       </c>
       <c r="B152" t="n">
-        <v>1338.216741264933</v>
+        <v>426.5861093605473</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3446,14 +3446,14 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1972</v>
+        <v>1958</v>
       </c>
       <c r="B153" t="n">
-        <v>217.6957407429651</v>
+        <v>442.5900830932796</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3469,10 +3469,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1972</v>
+        <v>1959</v>
       </c>
       <c r="B154" t="n">
-        <v>1256.316688096983</v>
+        <v>469.2512596112735</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -3492,14 +3492,14 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1972</v>
+        <v>1960</v>
       </c>
       <c r="B155" t="n">
-        <v>1474.012428839948</v>
+        <v>484.9322528829036</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3515,14 +3515,14 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1973</v>
+        <v>1961</v>
       </c>
       <c r="B156" t="n">
-        <v>255.4848400445016</v>
+        <v>503.2776347160874</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3538,10 +3538,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1973</v>
+        <v>1962</v>
       </c>
       <c r="B157" t="n">
-        <v>1429.560018309616</v>
+        <v>525.4492389980019</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -3561,14 +3561,14 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1973</v>
+        <v>1963</v>
       </c>
       <c r="B158" t="n">
-        <v>1685.044858354118</v>
+        <v>548.4317201515985</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3584,14 +3584,14 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1974</v>
+        <v>1964</v>
       </c>
       <c r="B159" t="n">
-        <v>305.8594920722974</v>
+        <v>584.416740608418</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3607,10 +3607,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1974</v>
+        <v>1965</v>
       </c>
       <c r="B160" t="n">
-        <v>1763.589689371715</v>
+        <v>629.5138499735924</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -3630,14 +3630,14 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1974</v>
+        <v>1966</v>
       </c>
       <c r="B161" t="n">
-        <v>2069.449181444013</v>
+        <v>689.3389442732511</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3653,14 +3653,14 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1975</v>
+        <v>1967</v>
       </c>
       <c r="B162" t="n">
-        <v>319.4743310918299</v>
+        <v>753.3311352268145</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3676,10 +3676,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1975</v>
+        <v>1968</v>
       </c>
       <c r="B163" t="n">
-        <v>1983.040821726274</v>
+        <v>835.8512661760232</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -3699,14 +3699,14 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1975</v>
+        <v>1969</v>
       </c>
       <c r="B164" t="n">
-        <v>2302.515152818104</v>
+        <v>928.3262407092185</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3722,14 +3722,14 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1976</v>
+        <v>1970</v>
       </c>
       <c r="B165" t="n">
-        <v>356.5855886169328</v>
+        <v>1032.410989618403</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -3745,10 +3745,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1976</v>
+        <v>1971</v>
       </c>
       <c r="B166" t="n">
-        <v>2204.961979321552</v>
+        <v>1145.856447448968</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -3768,14 +3768,14 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1976</v>
+        <v>1972</v>
       </c>
       <c r="B167" t="n">
-        <v>2561.547567938485</v>
+        <v>1256.316688096983</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3791,14 +3791,14 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1977</v>
+        <v>1973</v>
       </c>
       <c r="B168" t="n">
-        <v>402.9218074965217</v>
+        <v>1429.560018309616</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -3814,10 +3814,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1977</v>
+        <v>1974</v>
       </c>
       <c r="B169" t="n">
-        <v>2477.822211640865</v>
+        <v>1763.589689371715</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -3837,14 +3837,14 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="B170" t="n">
-        <v>2880.744019137386</v>
+        <v>1983.040821726274</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3860,14 +3860,14 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="B171" t="n">
-        <v>448.6215129892695</v>
+        <v>2204.961979321552</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -3883,10 +3883,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B172" t="n">
-        <v>2835.834184592632</v>
+        <v>2477.822211640865</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -3909,11 +3909,11 @@
         <v>1978</v>
       </c>
       <c r="B173" t="n">
-        <v>3284.455697581901</v>
+        <v>2835.834184592632</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3932,11 +3932,11 @@
         <v>1979</v>
       </c>
       <c r="B174" t="n">
-        <v>512.0243736088548</v>
+        <v>3283.947207948604</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -3952,10 +3952,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B175" t="n">
-        <v>3283.947207948604</v>
+        <v>3800.071121600247</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -3975,14 +3975,14 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B176" t="n">
-        <v>3795.971581557458</v>
+        <v>4326.983953050354</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -3998,14 +3998,14 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B177" t="n">
-        <v>555.6651749830419</v>
+        <v>4638.957776099302</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4021,10 +4021,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="B178" t="n">
-        <v>3800.071121600248</v>
+        <v>4822.675106371553</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -4044,14 +4044,14 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1980</v>
+        <v>1984</v>
       </c>
       <c r="B179" t="n">
-        <v>4355.736296583289</v>
+        <v>5136.971843292613</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4067,14 +4067,14 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1981</v>
+        <v>1985</v>
       </c>
       <c r="B180" t="n">
-        <v>618.2344737387148</v>
+        <v>5450.733993443455</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4090,10 +4090,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1981</v>
+        <v>1986</v>
       </c>
       <c r="B181" t="n">
-        <v>4326.983953050354</v>
+        <v>5739.714132823804</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -4113,14 +4113,14 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1981</v>
+        <v>1987</v>
       </c>
       <c r="B182" t="n">
-        <v>4945.218426789069</v>
+        <v>6092.19642781637</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4136,14 +4136,14 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1982</v>
+        <v>1988</v>
       </c>
       <c r="B183" t="n">
-        <v>632.4657606176995</v>
+        <v>6531.132870828345</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4159,10 +4159,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1982</v>
+        <v>1989</v>
       </c>
       <c r="B184" t="n">
-        <v>4638.957776099302</v>
+        <v>6967.269512947614</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -4182,14 +4182,14 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1982</v>
+        <v>1990</v>
       </c>
       <c r="B185" t="n">
-        <v>5271.423536717001</v>
+        <v>7416.819551621183</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4205,14 +4205,14 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1983</v>
+        <v>1991</v>
       </c>
       <c r="B186" t="n">
-        <v>673.2874813221468</v>
+        <v>7670.814119372146</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4228,10 +4228,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1983</v>
+        <v>1992</v>
       </c>
       <c r="B187" t="n">
-        <v>4822.675106371553</v>
+        <v>8013.034801142843</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -4251,14 +4251,14 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1983</v>
+        <v>1993</v>
       </c>
       <c r="B188" t="n">
-        <v>5495.9625876937</v>
+        <v>8456.679308939059</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4274,14 +4274,14 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="B189" t="n">
-        <v>745.4861043802233</v>
+        <v>8977.803393596974</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4297,10 +4297,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>1984</v>
+        <v>1995</v>
       </c>
       <c r="B190" t="n">
-        <v>5136.971843292613</v>
+        <v>9530.432697032011</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -4320,14 +4320,14 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1984</v>
+        <v>1996</v>
       </c>
       <c r="B191" t="n">
-        <v>5882.457947672836</v>
+        <v>10053.44780274493</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4343,14 +4343,14 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>1985</v>
+        <v>1997</v>
       </c>
       <c r="B192" t="n">
-        <v>816.6092674480941</v>
+        <v>10645.46761806427</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4366,10 +4366,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1985</v>
+        <v>1998</v>
       </c>
       <c r="B193" t="n">
-        <v>5450.733993443455</v>
+        <v>11273.09106570743</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -4389,14 +4389,14 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>1985</v>
+        <v>1999</v>
       </c>
       <c r="B194" t="n">
-        <v>6267.343260891549</v>
+        <v>11967.66739653786</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4412,14 +4412,14 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1986</v>
+        <v>2000</v>
       </c>
       <c r="B195" t="n">
-        <v>863.7334582791135</v>
+        <v>12840.56665694134</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4435,10 +4435,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>1986</v>
+        <v>2001</v>
       </c>
       <c r="B196" t="n">
-        <v>5739.714132823804</v>
+        <v>13620.73316634319</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -4458,14 +4458,14 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>1986</v>
+        <v>2002</v>
       </c>
       <c r="B197" t="n">
-        <v>6603.447591102918</v>
+        <v>14281.23387252014</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4481,14 +4481,14 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>1987</v>
+        <v>2003</v>
       </c>
       <c r="B198" t="n">
-        <v>1001.083527467324</v>
+        <v>14892.47915343409</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4504,10 +4504,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1987</v>
+        <v>2004</v>
       </c>
       <c r="B199" t="n">
-        <v>6092.19642781637</v>
+        <v>16199.66010837774</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -4527,14 +4527,14 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1987</v>
+        <v>2005</v>
       </c>
       <c r="B200" t="n">
-        <v>7093.279955283695</v>
+        <v>17723.46235535809</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4550,14 +4550,14 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1988</v>
+        <v>2006</v>
       </c>
       <c r="B201" t="n">
-        <v>1033.037216146162</v>
+        <v>19265.16196987102</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4573,10 +4573,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1988</v>
+        <v>2007</v>
       </c>
       <c r="B202" t="n">
-        <v>6531.132870828345</v>
+        <v>20353.55816995345</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -4596,14 +4596,14 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1988</v>
+        <v>2008</v>
       </c>
       <c r="B203" t="n">
-        <v>7564.170086974507</v>
+        <v>21776.88577520748</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4619,14 +4619,14 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>1989</v>
+        <v>2009</v>
       </c>
       <c r="B204" t="n">
-        <v>1085.42604844515</v>
+        <v>21294.71904053759</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4642,10 +4642,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1989</v>
+        <v>2010</v>
       </c>
       <c r="B205" t="n">
-        <v>6967.269512947614</v>
+        <v>21982.08196158394</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -4665,14 +4665,14 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1989</v>
+        <v>2011</v>
       </c>
       <c r="B206" t="n">
-        <v>8052.695561392764</v>
+        <v>23023.96860235302</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>XS009-C</t>
+          <t>XS009-B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4688,14 +4688,14 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1990</v>
+        <v>1946</v>
       </c>
       <c r="B207" t="n">
-        <v>1117.865976544959</v>
+        <v>173.2221675300687</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4711,14 +4711,14 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1990</v>
+        <v>1947</v>
       </c>
       <c r="B208" t="n">
-        <v>7416.819551621183</v>
+        <v>195.7752544758903</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -4734,10 +4734,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1990</v>
+        <v>1948</v>
       </c>
       <c r="B209" t="n">
-        <v>8534.685528166141</v>
+        <v>220.4816902446014</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -4757,14 +4757,14 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1991</v>
+        <v>1949</v>
       </c>
       <c r="B210" t="n">
-        <v>1136.620520775428</v>
+        <v>229.2275397818259</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -4780,14 +4780,14 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1991</v>
+        <v>1950</v>
       </c>
       <c r="B211" t="n">
-        <v>7670.814119372146</v>
+        <v>265.9043031913221</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -4803,10 +4803,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1991</v>
+        <v>1951</v>
       </c>
       <c r="B212" t="n">
-        <v>8807.434640147574</v>
+        <v>298.0863049648523</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -4826,14 +4826,14 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1992</v>
+        <v>1952</v>
       </c>
       <c r="B213" t="n">
-        <v>1197.206648206223</v>
+        <v>320.9804990944241</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -4849,14 +4849,14 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1992</v>
+        <v>1953</v>
       </c>
       <c r="B214" t="n">
-        <v>8013.034801142843</v>
+        <v>342.6366653886739</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -4872,10 +4872,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1992</v>
+        <v>1954</v>
       </c>
       <c r="B215" t="n">
-        <v>9210.241449349063</v>
+        <v>357.2725818091191</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -4895,14 +4895,14 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1993</v>
+        <v>1955</v>
       </c>
       <c r="B216" t="n">
-        <v>1248.180715356768</v>
+        <v>400.7672407784229</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -4918,14 +4918,14 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1993</v>
+        <v>1956</v>
       </c>
       <c r="B217" t="n">
-        <v>8456.679308939059</v>
+        <v>450.6755470664251</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -4941,10 +4941,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1993</v>
+        <v>1957</v>
       </c>
       <c r="B218" t="n">
-        <v>9704.860024295827</v>
+        <v>488.1419505731806</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -4964,14 +4964,14 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1994</v>
+        <v>1958</v>
       </c>
       <c r="B219" t="n">
-        <v>1497.309686291692</v>
+        <v>506.975278256839</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -4987,14 +4987,14 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1994</v>
+        <v>1959</v>
       </c>
       <c r="B220" t="n">
-        <v>8977.803393596974</v>
+        <v>541.1384504133814</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5010,10 +5010,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1994</v>
+        <v>1960</v>
       </c>
       <c r="B221" t="n">
-        <v>10475.11307988867</v>
+        <v>560.0638553376016</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -5033,14 +5033,14 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1995</v>
+        <v>1961</v>
       </c>
       <c r="B222" t="n">
-        <v>1398.771225589691</v>
+        <v>583.2290589182029</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5056,14 +5056,14 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1995</v>
+        <v>1962</v>
       </c>
       <c r="B223" t="n">
-        <v>9530.432697032011</v>
+        <v>611.0481523121117</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -5079,10 +5079,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1995</v>
+        <v>1963</v>
       </c>
       <c r="B224" t="n">
-        <v>10929.2039226217</v>
+        <v>640.7185491656269</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -5102,14 +5102,14 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1996</v>
+        <v>1964</v>
       </c>
       <c r="B225" t="n">
-        <v>1462.14304339995</v>
+        <v>683.1565505526382</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -5125,14 +5125,14 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1996</v>
+        <v>1965</v>
       </c>
       <c r="B226" t="n">
-        <v>10053.44780274493</v>
+        <v>740.1897503855342</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -5148,10 +5148,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1996</v>
+        <v>1966</v>
       </c>
       <c r="B227" t="n">
-        <v>11515.59084614488</v>
+        <v>813.6820802499406</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -5171,14 +5171,14 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1997</v>
+        <v>1967</v>
       </c>
       <c r="B228" t="n">
-        <v>1528.968573088737</v>
+        <v>890.5769407109261</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5194,14 +5194,14 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1997</v>
+        <v>1968</v>
       </c>
       <c r="B229" t="n">
-        <v>10645.46761806426</v>
+        <v>986.7243031773072</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1997</v>
+        <v>1969</v>
       </c>
       <c r="B230" t="n">
-        <v>12174.436191153</v>
+        <v>1099.480199838029</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -5240,14 +5240,14 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1998</v>
+        <v>1970</v>
       </c>
       <c r="B231" t="n">
-        <v>1584.041535971308</v>
+        <v>1212.96356178081</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5263,14 +5263,14 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1998</v>
+        <v>1971</v>
       </c>
       <c r="B232" t="n">
-        <v>11273.09106570743</v>
+        <v>1338.216741264933</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -5286,10 +5286,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1998</v>
+        <v>1972</v>
       </c>
       <c r="B233" t="n">
-        <v>12857.13260167873</v>
+        <v>1474.012428839948</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -5309,14 +5309,14 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1999</v>
+        <v>1973</v>
       </c>
       <c r="B234" t="n">
-        <v>1689.702679262337</v>
+        <v>1685.044858354118</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5332,14 +5332,14 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1999</v>
+        <v>1974</v>
       </c>
       <c r="B235" t="n">
-        <v>11967.66739653786</v>
+        <v>2069.449181444013</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -5355,10 +5355,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1999</v>
+        <v>1975</v>
       </c>
       <c r="B236" t="n">
-        <v>13657.3700758002</v>
+        <v>2302.515152818104</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -5378,14 +5378,14 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>2000</v>
+        <v>1976</v>
       </c>
       <c r="B237" t="n">
-        <v>1816.044686363544</v>
+        <v>2561.547567938485</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -5401,14 +5401,14 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2000</v>
+        <v>1977</v>
       </c>
       <c r="B238" t="n">
-        <v>12840.56665694134</v>
+        <v>2880.744019137386</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -5424,10 +5424,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2000</v>
+        <v>1978</v>
       </c>
       <c r="B239" t="n">
-        <v>14656.61134330488</v>
+        <v>3284.455697581901</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -5447,14 +5447,14 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>2001</v>
+        <v>1979</v>
       </c>
       <c r="B240" t="n">
-        <v>1786.616347218415</v>
+        <v>3795.971581557458</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5470,14 +5470,14 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>2001</v>
+        <v>1980</v>
       </c>
       <c r="B241" t="n">
-        <v>13620.73316634319</v>
+        <v>4355.736296583289</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -5493,10 +5493,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>2001</v>
+        <v>1981</v>
       </c>
       <c r="B242" t="n">
-        <v>15407.34951356161</v>
+        <v>4945.218426789069</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -5516,14 +5516,14 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>2002</v>
+        <v>1982</v>
       </c>
       <c r="B243" t="n">
-        <v>1874.073582251186</v>
+        <v>5271.423536717001</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -5539,14 +5539,14 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>2002</v>
+        <v>1983</v>
       </c>
       <c r="B244" t="n">
-        <v>14281.23387252014</v>
+        <v>5495.9625876937</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -5562,10 +5562,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>2002</v>
+        <v>1984</v>
       </c>
       <c r="B245" t="n">
-        <v>16155.30745477133</v>
+        <v>5882.457947672836</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -5585,14 +5585,14 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2003</v>
+        <v>1985</v>
       </c>
       <c r="B246" t="n">
-        <v>1978.6162598011</v>
+        <v>6267.343260891549</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -5608,14 +5608,14 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2003</v>
+        <v>1986</v>
       </c>
       <c r="B247" t="n">
-        <v>14892.47915343409</v>
+        <v>6603.447591102918</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -5631,10 +5631,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2003</v>
+        <v>1987</v>
       </c>
       <c r="B248" t="n">
-        <v>16871.09541323519</v>
+        <v>7093.279955283695</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -5654,14 +5654,14 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>2004</v>
+        <v>1988</v>
       </c>
       <c r="B249" t="n">
-        <v>2187.029189209532</v>
+        <v>7564.170086974507</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -5677,14 +5677,14 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>2004</v>
+        <v>1989</v>
       </c>
       <c r="B250" t="n">
-        <v>16199.66010837774</v>
+        <v>8052.695561392764</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -5700,10 +5700,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2004</v>
+        <v>1990</v>
       </c>
       <c r="B251" t="n">
-        <v>18386.68929758727</v>
+        <v>8534.685528166141</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -5723,14 +5723,14 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>2005</v>
+        <v>1991</v>
       </c>
       <c r="B252" t="n">
-        <v>2394.085629659626</v>
+        <v>8807.434640147574</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -5746,14 +5746,14 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>2005</v>
+        <v>1992</v>
       </c>
       <c r="B253" t="n">
-        <v>17723.46235535809</v>
+        <v>9210.241449349065</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -5769,10 +5769,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2005</v>
+        <v>1993</v>
       </c>
       <c r="B254" t="n">
-        <v>20117.54798501772</v>
+        <v>9704.860024295827</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -5792,14 +5792,14 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2006</v>
+        <v>1994</v>
       </c>
       <c r="B255" t="n">
-        <v>2578.091141691955</v>
+        <v>10475.11307988867</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -5815,14 +5815,14 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>2006</v>
+        <v>1995</v>
       </c>
       <c r="B256" t="n">
-        <v>19265.16196987102</v>
+        <v>10929.2039226217</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -5838,10 +5838,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>2006</v>
+        <v>1996</v>
       </c>
       <c r="B257" t="n">
-        <v>21843.25311156297</v>
+        <v>11515.59084614488</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -5861,14 +5861,14 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="B258" t="n">
-        <v>2676.214530237791</v>
+        <v>12174.436191153</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -5884,14 +5884,14 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>2007</v>
+        <v>1998</v>
       </c>
       <c r="B259" t="n">
-        <v>20353.55816995345</v>
+        <v>12857.13260167873</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -5907,10 +5907,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="B260" t="n">
-        <v>23029.77270019124</v>
+        <v>13657.3700758002</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -5930,14 +5930,14 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="B261" t="n">
-        <v>2675.893068192786</v>
+        <v>14656.61134330488</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -5953,14 +5953,14 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="B262" t="n">
-        <v>21776.88577520748</v>
+        <v>15407.34951356161</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -5976,10 +5976,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="B263" t="n">
-        <v>24452.77884340027</v>
+        <v>16155.30745477133</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -5999,14 +5999,14 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="B264" t="n">
-        <v>2562.064159856566</v>
+        <v>16871.09541323519</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -6022,14 +6022,14 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="B265" t="n">
-        <v>21294.71904053759</v>
+        <v>18386.68929758727</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -6045,10 +6045,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="B266" t="n">
-        <v>23856.78320039415</v>
+        <v>20117.54798501772</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -6068,14 +6068,14 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="B267" t="n">
-        <v>2726.997261674907</v>
+        <v>21843.25311156298</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -6091,14 +6091,14 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="B268" t="n">
-        <v>21982.08196158393</v>
+        <v>23029.77270019124</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -6114,10 +6114,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B269" t="n">
-        <v>24709.07922325884</v>
+        <v>24452.77884340027</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -6137,14 +6137,14 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B270" t="n">
-        <v>2937.530680167656</v>
+        <v>23856.78320039415</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>XS009-A</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -6160,14 +6160,14 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B271" t="n">
-        <v>23023.96860235302</v>
+        <v>24709.07922325884</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>XS009-B</t>
+          <t>XS009-C</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -6216,7 +6216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A94"/>
+  <dimension ref="A1:A96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -6292,7 +6292,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Source: Appendix Table 6.8.II.6. UNIT NORMALIZATION: raw IRS SOI INVIRScorp is in thousands of dollars and divided by 1000 at load time. Per Phase 4 Q3: extension_method='constant_ratio_proxy_2012_onwards' flag carried through; Phase 6 lift to re-estimated ratio is recommended but deferred. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+          <t>Source: Shaikh (2016), Appendix Table 6.8.II.6. Unit normalization: the raw IRS Statistics of Income (SOI) inventory line is in thousands of dollars, but Shaikh's Appendix Table 6.8.II.6 column `INVcorp` is already rescaled to billions of current USD; the loader reads that Appendix column with **scale = 1.0 — no division at load time**. An extension flag (`extension_method = 'constant_ratio_proxy_2012_onwards'`) is carried through; a later lift to a re-estimated ratio is recommended but deferred.</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>## Sources (per subseries)</t>
+          <t>&gt; **Correction (2026-07-02, DF-2):** the earlier "divided by 1000 at load time" phrasing was inaccurate — the loader applies scale = 1.0 because the Appendix source column is already in billions. The same "/1000" phrasing in the series-registry `notes`/`params` for XS009 (and the "XS007/XS009 apply /1000" mention) is registry-side and left for the registry owner to reconcile.</t>
         </is>
       </c>
     </row>
@@ -6312,45 +6312,45 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>| Subseries | Appendix Table | Variable | Source agency | Notes |</t>
+          <t>## Sources (per subseries)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>|-----------|---------------|----------|---------------|-------|</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>| XS009-A | II6 | `INVcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| Subseries | Appendix Table | Variable | Source agency | Notes |</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>| XS009-B | II6 | `KGCcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>|-----------|---------------|----------|---------------|-------|</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>| XS009-C | II6 | `KTCcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| XS009-A | II6 | `INVcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>| XS009-B | II6 | `KGCcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
+          <t>| XS009-C | II6 | `KTCcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>The `-A`, `-B`, and `-C` suffixes label the individual sub-variants of this series. The canonical Shaikh-published values are transcribed from the published Chapter 6 appendix workbook (Shaikh 2016, Appendix 6.8). Upstream agencies are the Bureau of Economic Analysis (BEA) — its National Income and Product Accounts (NIPA) and Fixed Asset accounts (FA) — the IRS Statistics of Income (SOI), the U.S. Census Bureau Historical Statistics 1975 (IRS book values), and the Federal Reserve Board G.17 release. All public domain.</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6370,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INVcorp = IRS SOI corporate inventories at current cost. KTCcorp = KGCcorp (from XS004) + INVcorp. Raw IRS SOI inventory line is in THOUSANDS OF DOLLARS in the upstream IRS source; Shaikh's Appendix Table 6.8.II.6 column INVcorp is already in billions of current USD after Shaikh's rescaling. Post-2011 inventory is bounded by IRS reporting; constant-ratio proxy flagged via `extension_method: constant_ratio_proxy_2012_onwards`.</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>## Year Coverage</t>
+          <t>INVcorp = IRS SOI corporate inventories at current cost. KTCcorp = KGCcorp (from XS004) + INVcorp. Raw IRS SOI inventory line is in THOUSANDS OF DOLLARS in the upstream IRS source; Shaikh's Appendix Table 6.8.II.6 column INVcorp is already in billions of current USD after Shaikh's rescaling. Post-2011 inventory is bounded by IRS reporting; constant-ratio proxy flagged via `extension_method: constant_ratio_proxy_2012_onwards`.</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6390,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Book period: 1946-2011. Vintage-stable extension recipe in `XS009_EPR.md`.</t>
+          <t>## Year Coverage</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>## Units</t>
+          <t>Book period: 1946-2011. See the companion Extension Provenance Record for the vintage-stable extension recipe.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>## Units</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>## Caveats</t>
+          <t>billions_current_usd</t>
         </is>
       </c>
     </row>
@@ -6430,24 +6430,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>## Caveats</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>* Raw IRS SOI inventories in thousands of dollars; INVcorp column in Appendix Table 6.8.II.6 is already rescaled to billions.</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>* Post-2011 inventory uses constant 2011 ratio proxy; flagged via `extension_method`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>## Cross-references</t>
+          <t>* Post-2011 inventory uses constant 2011 ratio proxy; flagged via `extension_method`.</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>## Cross-references</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>## Validation Expectation</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
@@ -6477,30 +6477,30 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>`V03_XS009_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4">
+          <t>## Validation Expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>The series round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Two construction dependencies are resolved: the remapping of the NIPA Table 7.11 financial services indirectly measured (FISIM) lines, and the BEA 1993 depreciation rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4">
         <f>== EPR: XS009_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t># XS009 — IRS Corporate Inventories and Total Capital Stock (Extension Provenance Record)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-    </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>**Classification:** feasible_with_proxy_or_substitute  **Tolerance for extended values:** 1.0%</t>
+          <t># XS009 — IRS Corporate Inventories and Total Capital Stock (Extension Provenance Record)</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6510,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>## Method</t>
+          <t>**Classification:** feasible_with_proxy_or_substitute  **Tolerance for extended values:** 1.0%</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published XS009 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
+          <t>## Method</t>
         </is>
       </c>
     </row>
@@ -6530,38 +6530,38 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+          <t>Following the Chapter 6 Generalized Perpetual Inventory Method (GPIM) construction pipeline and the project's anti-degradation rule, **extension does NOT splice the published XS009 values**. Instead, the extension re-fetches the underlying National Income and Product Accounts (NIPA), BEA Fixed Asset, IRS, and Census components and re-runs the formula end-to-end at the current vintage.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3. Re-run the construction formula end-to-end.</t>
+          <t>1. Fetch the BEA NIPA tables from the BEA API (a BEA API key is required) using the documented primary-source table ids.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4. Post-2011 inventory currently uses `extension_method: constant_ratio_proxy_2012_onwards`. Phase 6 lift recommended: re-estimate INV/KGC ratio from current IRS SOI Corporation Complete Report (https://www.irs.gov/statistics/soi-tax-stats-corporation-complete-report) using BEA FA T6.3 historical-cost stock as the denominator.</t>
+          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 from the same source.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>3. Re-run the construction formula end-to-end.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>## Worked Example</t>
+          <t>4. Post-2011 inventory currently uses the `constant_ratio_proxy_2012_onwards` extension method. A later lift is recommended: re-estimate the INV/KGC ratio from the current IRS SOI Corporation Complete Report (https://www.irs.gov/statistics/soi-tax-stats-corporation-complete-report) using the BEA Fixed Asset Table 6.3 historical-cost stock as the denominator.</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>For XS009, the Phase 5 round-trip validation reads `XS009_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1946-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+          <t>## Worked Example</t>
         </is>
       </c>
     </row>
@@ -6581,7 +6581,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>## No-Proxy Disclosure</t>
+          <t>For XS009, the round-trip validation reads the raw values from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1946-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>No proxies are used in the book period. XS009 carries an extension-only proxy flag (constant_ratio_proxy_2012_onwards); see Decision 0002 + Phase 4 Q3.</t>
+          <t>## Proxy Use</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>## No-Synthetic Disclosure</t>
+          <t>No proxies are used in the book period. XS009 carries an extension-only proxy flag (`constant_ratio_proxy_2012_onwards`).</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+          <t>## Synthetic Values</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>## Failure Mode Table</t>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified against the reconstructed BEA 1993 staged inputs).</t>
         </is>
       </c>
     </row>
@@ -6631,59 +6631,59 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Response |</t>
+          <t>## Failure Mode Table</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>|---------|-----------|----------|</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+          <t>| Failure | Detection | Response |</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>|---------|-----------|----------|</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+          <t>| Appendix workbook missing or corrupted | The appendix loader raises a file-not-found error or returns an empty table | Loading fails with an explicit error |</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (XS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>| Variable name not in workbook | The variable lookup returns no rows | Zero rows are recorded for that subseries and validation flags it as missing |</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
+          <t>| BEA / IRS vintage drift during extension | The re-fetch logs the vintage year; validation tolerance widens for extension rows | Documented per-year; no silent overwrite of the book period |</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>| NIPA Table 7.11 financial services indirectly measured (FISIM) line revision (affecting XS003) | The line resolver falls back to the nearest pinned vintage with a logged warning | Re-mapped by label; vintage logged |</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
+          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation-rate inputs at 2011-vintage projection | Documented with the reconstructed BEA 1993 Fixed Asset methodology inputs |</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CD2 S214 INVIRScorp raw values are also ~1000x larger; same normalization applies. Post-2011 proxy is explicitly flagged via `extension_method` metadata.</t>
+          <t>## Divergence From an Earlier Replication</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>## Anti-Degradation Compliance</t>
+          <t>In an earlier replication the raw inventory values were also ~1000× larger; the same normalization applies. The post-2011 proxy is explicitly flagged via the `extension_method` metadata.</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
+          <t>## Extension Integrity</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Extension must re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end; splicing the published series is not permitted. Fetched BEA / FRED responses are cached with a 30-day time-to-live (book-period values are cached permanently).</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7082,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:51:22.915744+00:00</t>
+          <t>2026-07-02T06:28:54.429213+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS009_extenbook.xlsx
+++ b/extenbooks/XS009_extenbook.xlsx
@@ -7082,7 +7082,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:28:54.429213+00:00</t>
+          <t>2026-07-11T03:44:27.660013+00:00</t>
         </is>
       </c>
     </row>
@@ -7097,11 +7097,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7124,6 +7124,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Adds IRS corporate inventories to GPIM gross fixed capital to form total corporate capital stock (KTC = KGC + INV), the denominator of the corrected profit rate. All billions_current_usd after the documented IRS thousands-to-billions normalization; single-unit, renders sensibly. Appendix Table 6.8.II.6.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS009_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS009_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Source: Appendix Table 6.8.II.6 (INVcorp, KGCcorp, KTCcorp). These values are already in billions of current USD and are loaded with scale=1.0 - NO /1000 normalization is applied (corrected 2026-07-02, SWEEP-ch05_ch06_xsapx: the prior note falsely claimed a thousands-&gt;billions /1000 division; the loader SOURCE_MAP scale is 1.0). Per Phase 4 Q3: extension_method='constant_ratio_proxy_2012_onwards' flag carried through; Phase 6 lift to re-estimated ratio is recommended but deferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>billions_current_usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
